--- a/InputData/trans/AVLo/Avg Vehicle Loading.xlsx
+++ b/InputData/trans/AVLo/Avg Vehicle Loading.xlsx
@@ -1,33 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\AVLo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/trans/AVLo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B446D3AE-B87D-4E62-AC29-BC99054FBCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B446D3AE-B87D-4E62-AC29-BC99054FBCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{907C920D-B501-4A38-8AC2-693D8D344339}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BTS NTS Modal Profile Data" sheetId="3" r:id="rId2"/>
-    <sheet name="AVLo-passengers" sheetId="2" r:id="rId3"/>
-    <sheet name="AVLo-freight" sheetId="4" r:id="rId4"/>
+    <sheet name="SYAVLo-passengers" sheetId="5" r:id="rId3"/>
+    <sheet name="SYAVLo-freight" sheetId="6" r:id="rId4"/>
+    <sheet name="AVLo-passengers" sheetId="2" r:id="rId5"/>
+    <sheet name="AVLo-freight" sheetId="4" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="Eno_TM">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
     <definedName name="Sum_T2">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="ti_tbl_50">#REF!</definedName>
     <definedName name="ti_tbl_69">#REF!</definedName>
+    <definedName name="TitleRegion1.f2.y3.5">#REF!</definedName>
+    <definedName name="TitleRegion1.f3.n4.5">#REF!</definedName>
+    <definedName name="TitleRegion2.e6.y15.5">#REF!</definedName>
+    <definedName name="TitleRegion2.e8.n17.5">#REF!</definedName>
+    <definedName name="TitleRegion3.c19.y51.5">#REF!</definedName>
+    <definedName name="TitleRegion3.c24.n53.5">#REF!</definedName>
+    <definedName name="TitleRegion4.e54.y63.5">#REF!</definedName>
+    <definedName name="TitleRegion4.e57.n66.5">#REF!</definedName>
+    <definedName name="TitleRegion5.d68.y124.5">#REF!</definedName>
+    <definedName name="TitleRegion5.d73.n129.5">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="116">
   <si>
     <t>AVLo Average Vehicle Loading</t>
   </si>
@@ -1467,7 +1481,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Rail shipments 93-97"/>
@@ -1547,10 +1561,42 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="BTS NTS Modal Profile Data"/>
+      <sheetName val="Annual Service Data_rail only"/>
+      <sheetName val="Fuel and Energy_rail only"/>
+      <sheetName val="psgr rail calcs"/>
+      <sheetName val="SYAVLo-passengers"/>
+      <sheetName val="SYAVLo-freight"/>
+      <sheetName val="AVLo-passengers"/>
+      <sheetName val="AVLo-freight"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1588,9 +1634,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1623,26 +1669,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1675,26 +1704,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1869,10 +1881,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" customWidth="1"/>
-    <col min="2" max="2" width="85.08984375" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="85.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2139,11 +2151,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C69"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="73.6328125" customWidth="1"/>
+    <col min="1" max="1" width="73.5703125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="102.26953125" customWidth="1"/>
+    <col min="3" max="3" width="102.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2658,279 +2670,34 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D02CBB-652F-4432-9C85-31046D398032}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="43.5">
+    <row r="1" spans="1:2" ht="45">
       <c r="A1" s="16" t="s">
         <v>111</v>
       </c>
       <c r="B1" s="5">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="5">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="5">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="H1" s="5">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="5">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="5">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-      <c r="N1" s="5">
-        <v>2027</v>
-      </c>
-      <c r="O1" s="1">
-        <v>2028</v>
-      </c>
-      <c r="P1" s="5">
-        <v>2029</v>
-      </c>
-      <c r="Q1" s="1">
-        <v>2030</v>
-      </c>
-      <c r="R1" s="5">
-        <v>2031</v>
-      </c>
-      <c r="S1" s="1">
-        <v>2032</v>
-      </c>
-      <c r="T1" s="5">
-        <v>2033</v>
-      </c>
-      <c r="U1" s="1">
-        <v>2034</v>
-      </c>
-      <c r="V1" s="5">
-        <v>2035</v>
-      </c>
-      <c r="W1" s="1">
-        <v>2036</v>
-      </c>
-      <c r="X1" s="5">
-        <v>2037</v>
-      </c>
-      <c r="Y1" s="1">
-        <v>2038</v>
-      </c>
-      <c r="Z1" s="5">
-        <v>2039</v>
-      </c>
-      <c r="AA1" s="1">
-        <v>2040</v>
-      </c>
-      <c r="AB1" s="5">
-        <v>2041</v>
-      </c>
-      <c r="AC1" s="1">
-        <v>2042</v>
-      </c>
-      <c r="AD1" s="5">
-        <v>2043</v>
-      </c>
-      <c r="AE1" s="1">
-        <v>2044</v>
-      </c>
-      <c r="AF1" s="5">
-        <v>2045</v>
-      </c>
-      <c r="AG1" s="1">
-        <v>2046</v>
-      </c>
-      <c r="AH1" s="5">
-        <v>2047</v>
-      </c>
-      <c r="AI1" s="1">
-        <v>2048</v>
-      </c>
-      <c r="AJ1" s="5">
-        <v>2049</v>
-      </c>
-      <c r="AK1" s="1">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37">
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="7">
         <v>1.67</v>
       </c>
-      <c r="C2" s="7">
-        <f>$B2</f>
-        <v>1.67</v>
-      </c>
-      <c r="D2" s="7">
-        <f t="shared" ref="D2:AK7" si="0">$B2</f>
-        <v>1.67</v>
-      </c>
-      <c r="E2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="F2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="G2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="H2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="I2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="J2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="K2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="L2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="M2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="N2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="O2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="P2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="Q2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="R2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="S2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="T2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="U2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="V2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="W2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="X2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="Y2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="Z2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AA2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AB2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AC2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AD2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AE2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AF2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AG2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AH2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AI2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AJ2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-      <c r="AK2" s="7">
-        <f t="shared" si="0"/>
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2938,148 +2705,8 @@
         <f>'BTS NTS Modal Profile Data'!B14</f>
         <v>21.196137258578663</v>
       </c>
-      <c r="C3" s="7">
-        <f t="shared" ref="C3:R7" si="1">$B3</f>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="D3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="E3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="F3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="G3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="H3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="I3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="J3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="K3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="L3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="M3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="N3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="O3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="P3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="Q3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="R3" s="7">
-        <f t="shared" si="1"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="S3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="T3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="U3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="V3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="W3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="X3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="Y3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="Z3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AA3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AB3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AC3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AD3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AE3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AF3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AG3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AH3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AI3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AJ3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-      <c r="AK3" s="7">
-        <f t="shared" si="0"/>
-        <v>21.196137258578663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -3087,148 +2714,8 @@
         <f>'BTS NTS Modal Profile Data'!B8</f>
         <v>111.39416306433705</v>
       </c>
-      <c r="C4" s="7">
-        <f t="shared" si="1"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="D4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="E4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="F4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="G4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="H4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="I4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="J4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="K4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="L4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="M4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="N4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="O4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="P4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="Q4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="R4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="S4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="T4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="U4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="V4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="W4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="X4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="Y4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="Z4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AA4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AB4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AC4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AD4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AE4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AF4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AG4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AH4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AI4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AJ4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-      <c r="AK4" s="7">
-        <f t="shared" si="0"/>
-        <v>111.39416306433705</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -3236,441 +2723,21 @@
         <f>'BTS NTS Modal Profile Data'!B37</f>
         <v>486.56731685074101</v>
       </c>
-      <c r="C5" s="7">
-        <f t="shared" si="1"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="D5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="M5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="N5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="O5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="P5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="Q5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="R5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="S5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="T5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="U5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="V5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="W5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="X5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="Y5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="Z5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AA5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AB5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AC5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AD5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AE5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AF5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AG5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AH5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AI5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AJ5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-      <c r="AK5" s="7">
-        <f t="shared" si="0"/>
-        <v>486.56731685074101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="7">
         <v>1</v>
       </c>
-      <c r="C6" s="7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="D6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="P6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="R6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="S6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="T6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="U6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="V6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="W6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Z6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AA6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AB6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AC6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AD6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AE6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AF6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AG6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AH6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AI6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="AK6" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="7">
         <f>'BTS NTS Modal Profile Data'!B60</f>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="C7" s="7">
-        <f t="shared" si="1"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="D7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="E7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="F7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="G7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="H7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="I7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="K7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="L7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="M7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="N7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="O7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="P7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="Q7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="R7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="S7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="T7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="U7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="V7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="W7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="X7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="Y7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="Z7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AA7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AB7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AC7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AD7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AE7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AF7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AG7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AH7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AI7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AJ7" s="7">
-        <f t="shared" si="0"/>
-        <v>1.2700756740871355</v>
-      </c>
-      <c r="AK7" s="7">
-        <f t="shared" si="0"/>
         <v>1.2700756740871355</v>
       </c>
     </row>
@@ -3680,17 +2747,1115 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8322D320-1FB8-4B15-A9ED-2D9DDBA8E003}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="45">
+      <c r="A1" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="6">
+        <f>'BTS NTS Modal Profile Data'!B9</f>
+        <v>41.989116133258747</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="6">
+        <f>'BTS NTS Modal Profile Data'!B19</f>
+        <v>3512.35916421195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6">
+        <f>'BTS NTS Modal Profile Data'!B55</f>
+        <v>1974.4736422180429</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AK7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" ht="45">
+      <c r="A1" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="5">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="5">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="5">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="5">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="5">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="5">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+      <c r="N1" s="5">
+        <v>2027</v>
+      </c>
+      <c r="O1" s="1">
+        <v>2028</v>
+      </c>
+      <c r="P1" s="5">
+        <v>2029</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>2030</v>
+      </c>
+      <c r="R1" s="5">
+        <v>2031</v>
+      </c>
+      <c r="S1" s="1">
+        <v>2032</v>
+      </c>
+      <c r="T1" s="5">
+        <v>2033</v>
+      </c>
+      <c r="U1" s="1">
+        <v>2034</v>
+      </c>
+      <c r="V1" s="5">
+        <v>2035</v>
+      </c>
+      <c r="W1" s="1">
+        <v>2036</v>
+      </c>
+      <c r="X1" s="5">
+        <v>2037</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>2038</v>
+      </c>
+      <c r="Z1" s="5">
+        <v>2039</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>2040</v>
+      </c>
+      <c r="AB1" s="5">
+        <v>2041</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>2042</v>
+      </c>
+      <c r="AD1" s="5">
+        <v>2043</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>2044</v>
+      </c>
+      <c r="AF1" s="5">
+        <v>2045</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>2046</v>
+      </c>
+      <c r="AH1" s="5">
+        <v>2047</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>2048</v>
+      </c>
+      <c r="AJ1" s="5">
+        <v>2049</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1.67</v>
+      </c>
+      <c r="C2" s="7">
+        <f>$B2</f>
+        <v>1.67</v>
+      </c>
+      <c r="D2" s="7">
+        <f t="shared" ref="D2:AK7" si="0">$B2</f>
+        <v>1.67</v>
+      </c>
+      <c r="E2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="F2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="G2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="H2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="I2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="J2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="K2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="L2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="M2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="O2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="P2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="Q2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="R2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="S2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="T2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="U2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="V2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="W2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="X2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="Y2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="Z2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AA2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AB2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AC2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AD2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AE2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AF2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AG2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AH2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AI2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AJ2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+      <c r="AK2" s="7">
+        <f t="shared" si="0"/>
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="9">
+        <f>'BTS NTS Modal Profile Data'!B14</f>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="C3" s="7">
+        <f t="shared" ref="C3:R7" si="1">$B3</f>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="D3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="E3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="F3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="G3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="H3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="J3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="L3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="P3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="Q3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="R3" s="7">
+        <f t="shared" si="1"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="S3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="T3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="U3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="V3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="W3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="X3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="Y3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="Z3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AA3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AB3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AC3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AD3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AE3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AF3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AG3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AH3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AI3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AJ3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+      <c r="AK3" s="7">
+        <f t="shared" si="0"/>
+        <v>21.196137258578663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="9">
+        <f>'BTS NTS Modal Profile Data'!B8</f>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="C4" s="7">
+        <f t="shared" si="1"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="G4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="J4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="P4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="Q4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="R4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="S4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="T4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="U4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="V4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="W4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="X4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="Y4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="Z4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AA4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AB4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AC4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AD4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AE4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AF4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AG4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AH4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AI4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AJ4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+      <c r="AK4" s="7">
+        <f t="shared" si="0"/>
+        <v>111.39416306433705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="9">
+        <f>'BTS NTS Modal Profile Data'!B37</f>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="C5" s="7">
+        <f t="shared" si="1"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="R5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="S5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="T5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="U5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="V5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="W5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="X5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="Y5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="Z5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AA5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AB5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AC5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AD5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AE5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AF5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AG5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AH5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AI5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AJ5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+      <c r="AK5" s="7">
+        <f t="shared" si="0"/>
+        <v>486.56731685074101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="S6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="U6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="W6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Z6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AA6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AB6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AC6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AD6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AE6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AF6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AG6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK6" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="7">
+        <f>'BTS NTS Modal Profile Data'!B60</f>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="C7" s="7">
+        <f t="shared" si="1"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="D7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="P7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="Q7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="R7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="S7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="T7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="U7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="V7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="W7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="X7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="Y7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="Z7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AA7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AB7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AC7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AD7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AE7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AF7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AG7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AH7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AI7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AJ7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+      <c r="AK7" s="7">
+        <f t="shared" si="0"/>
+        <v>1.2700756740871355</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" ht="43.5">
+    <row r="1" spans="1:36" s="1" customFormat="1" ht="45">
       <c r="A1" s="16" t="s">
         <v>112</v>
       </c>
@@ -4671,4 +4836,198 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{095C30AA-153C-422C-9EAC-F606F12FEB6D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F2DB2DA-7479-48A8-B4C3-19CBB24DF7C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AF3F849-BFF6-4A96-AD9C-527D539A379F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>